--- a/publish/StructureDefinition-NoDomainVitalSignsMethodofOxygenDeliveryExtension.xlsx
+++ b/publish/StructureDefinition-NoDomainVitalSignsMethodofOxygenDeliveryExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-10T16:24:07+00:00</t>
+    <t>2026-03-13T10:43:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/publish/StructureDefinition-NoDomainVitalSignsMethodofOxygenDeliveryExtension.xlsx
+++ b/publish/StructureDefinition-NoDomainVitalSignsMethodofOxygenDeliveryExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.74</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T10:43:11+00:00</t>
+    <t>2025-11-20T10:22:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/publish/StructureDefinition-NoDomainVitalSignsMethodofOxygenDeliveryExtension.xlsx
+++ b/publish/StructureDefinition-NoDomainVitalSignsMethodofOxygenDeliveryExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T10:22:37+00:00</t>
+    <t>2026-03-13T10:43:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
